--- a/Configs/GameConfig/Datas/Combat.xlsx
+++ b/Configs/GameConfig/Datas/Combat.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleConfig" sheetId="1" r:id="R0a56a5d99b764f29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttackConfig" sheetId="2" r:id="Rac0219791fc94de8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleConfig" sheetId="1" r:id="R58932a40fa4843f4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AttackConfig" sheetId="2" r:id="R51b50fa754e244a8"/>
   </sheets>
 </workbook>
 </file>
@@ -318,104 +318,84 @@
         <v>MdefK_Hero</v>
       </c>
       <c r="F1" s="1" t="str">
-        <v>MissK_Hero</v>
+        <v>DefK_Monster</v>
       </c>
       <c r="G1" s="1" t="str">
-        <v>DefK_Monster</v>
+        <v>MdefK_Monster</v>
       </c>
       <c r="H1" s="1" t="str">
-        <v>MdefK_Monster</v>
+        <v>LuckyK_HeroAtk</v>
       </c>
       <c r="I1" s="1" t="str">
-        <v>MissK_Monster</v>
+        <v>LuckyK_MonsterAtk</v>
       </c>
       <c r="J1" s="1" t="str">
-        <v>CritK</v>
+        <v>CritBase</v>
       </c>
       <c r="K1" s="1" t="str">
-        <v>LuckyK_HeroAtk</v>
+        <v>LvLuckyCoef</v>
       </c>
       <c r="L1" s="1" t="str">
-        <v>LuckyK_MonsterAtk</v>
+        <v>LvDamageCoef</v>
       </c>
       <c r="M1" s="1" t="str">
-        <v>CritBase</v>
+        <v>LvLuckyCap</v>
       </c>
       <c r="N1" s="1" t="str">
-        <v>LvMissCoef_HeroDef</v>
+        <v>LvDamageCapLv_HeroDef</v>
       </c>
       <c r="O1" s="1" t="str">
-        <v>LvCritCoef_HeroDef</v>
+        <v>LvDamageCapLv_MonsterDef</v>
       </c>
       <c r="P1" s="1" t="str">
-        <v>LvMissCoef_MonsterDef</v>
-      </c>
-      <c r="Q1" s="1" t="str">
-        <v>LvCritCoef_MonsterDef</v>
-      </c>
-      <c r="R1" s="1" t="str">
-        <v>LvLuckyCoef</v>
-      </c>
-      <c r="S1" s="1" t="str">
-        <v>LvDamageCoef</v>
-      </c>
-      <c r="T1" s="1" t="str">
-        <v>LvMissCap_HeroDef</v>
-      </c>
-      <c r="U1" s="1" t="str">
-        <v>LvMissCap_MonsterDef</v>
-      </c>
-      <c r="V1" s="1" t="str">
-        <v>LvCritCap</v>
-      </c>
-      <c r="W1" s="1" t="str">
-        <v>LvLuckyCap</v>
-      </c>
-      <c r="X1" s="1" t="str">
-        <v>LvDamageCapLv_HeroDef</v>
-      </c>
-      <c r="Y1" s="1" t="str">
-        <v>LvDamageCapLv_MonsterDef</v>
-      </c>
-      <c r="Z1" s="1" t="str">
         <v>WsMax</v>
       </c>
+      <c r="Q1" s="2" t="str">
+        <v>WsGainPerDamageRatio</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>WsAttackMultiplier</v>
+      </c>
+      <c r="S1" s="2" t="str">
+        <v>WsMoveSpeedMultiplier</v>
+      </c>
+      <c r="T1" s="2" t="str">
+        <v>WsJumpSpeedMultiplier</v>
+      </c>
+      <c r="U1" s="2" t="str">
+        <v>WsGravityMultiplier</v>
+      </c>
+      <c r="V1" s="2" t="str">
+        <v>WsDecayPerSecond</v>
+      </c>
+      <c r="W1" s="2" t="str">
+        <v>WsDrainPerSecond</v>
+      </c>
+      <c r="X1" s="2" t="str">
+        <v>MonsterKnockbackRetentionPerSecond</v>
+      </c>
+      <c r="Y1" s="2" t="str">
+        <v>MusouPerOrb</v>
+      </c>
+      <c r="Z1" s="2" t="str">
+        <v>ManaMinimum</v>
+      </c>
       <c r="AA1" s="2" t="str">
-        <v>WsGainPerDamageRatio</v>
+        <v>ManaMaxFraction</v>
       </c>
       <c r="AB1" s="2" t="str">
-        <v>WsAttackMultiplier</v>
-      </c>
-      <c r="AC1" s="2" t="str">
-        <v>WsMoveSpeedMultiplier</v>
-      </c>
-      <c r="AD1" s="2" t="str">
-        <v>WsJumpSpeedMultiplier</v>
-      </c>
-      <c r="AE1" s="2" t="str">
-        <v>WsGravityMultiplier</v>
-      </c>
-      <c r="AF1" s="2" t="str">
-        <v>WsDecayPerSecond</v>
-      </c>
-      <c r="AG1" s="2" t="str">
-        <v>WsDrainPerSecond</v>
-      </c>
-      <c r="AH1" s="2" t="str">
-        <v>MonsterKnockbackRetentionPerSecond</v>
-      </c>
-      <c r="AI1" s="2" t="str">
-        <v>MusouPerOrb</v>
-      </c>
-      <c r="AJ1" s="2" t="str">
-        <v>ManaMinimum</v>
-      </c>
-      <c r="AK1" s="2" t="str">
-        <v>ManaMaxFraction</v>
-      </c>
-      <c r="AL1" s="2" t="str">
         <v>GroundLifetime</v>
       </c>
+      <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
+      <c r="AF1"/>
+      <c r="AG1"/>
+      <c r="AH1"/>
+      <c r="AI1"/>
+      <c r="AJ1"/>
+      <c r="AK1"/>
+      <c r="AL1"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="1" t="str">
@@ -436,28 +416,28 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
       <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
       <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="1" t="str">
@@ -500,42 +480,42 @@
         <v>float</v>
       </c>
       <c r="N3" s="1" t="str">
+        <v>int</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <v>int</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <v>int</v>
+      </c>
+      <c r="Q3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="O3" s="1" t="str">
+      <c r="R3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="P3" s="1" t="str">
+      <c r="S3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="Q3" s="1" t="str">
+      <c r="T3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="R3" s="1" t="str">
+      <c r="U3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="S3" s="1" t="str">
+      <c r="V3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="T3" s="1" t="str">
+      <c r="W3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="U3" s="1" t="str">
+      <c r="X3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="V3" s="1" t="str">
-        <v>float</v>
-      </c>
-      <c r="W3" s="1" t="str">
-        <v>float</v>
-      </c>
-      <c r="X3" s="1" t="str">
+      <c r="Y3" s="2" t="str">
         <v>int</v>
       </c>
-      <c r="Y3" s="1" t="str">
-        <v>int</v>
-      </c>
-      <c r="Z3" s="1" t="str">
+      <c r="Z3" s="2" t="str">
         <v>int</v>
       </c>
       <c r="AA3" s="2" t="str">
@@ -544,36 +524,16 @@
       <c r="AB3" s="2" t="str">
         <v>float</v>
       </c>
-      <c r="AC3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AD3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AE3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AF3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AG3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AH3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AI3" s="2" t="str">
-        <v>int</v>
-      </c>
-      <c r="AJ3" s="2" t="str">
-        <v>int</v>
-      </c>
-      <c r="AK3" s="2" t="str">
-        <v>float</v>
-      </c>
-      <c r="AL3" s="2" t="str">
-        <v>float</v>
-      </c>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="1" t="str">
@@ -594,28 +554,28 @@
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
       <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-      <c r="AD4" s="2"/>
-      <c r="AE4" s="2"/>
-      <c r="AF4" s="2"/>
-      <c r="AG4" s="2"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="2"/>
-      <c r="AJ4" s="2"/>
-      <c r="AK4" s="2"/>
-      <c r="AL4" s="2"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="1" t="str">
@@ -634,104 +594,84 @@
         <v>英雄作防守方时魔防减伤K</v>
       </c>
       <c r="F5" s="1" t="str">
-        <v>英雄作防守方时被命中K: Miss/(Miss+K)</v>
+        <v>怪物作防守方时物防减伤K</v>
       </c>
       <c r="G5" s="1" t="str">
-        <v>怪物作防守方时物防减伤K</v>
+        <v>怪物作防守方时魔防减伤K</v>
       </c>
       <c r="H5" s="1" t="str">
-        <v>怪物作防守方时魔防减伤K</v>
+        <v>英雄攻击时暴击倍率幸运K</v>
       </c>
       <c r="I5" s="1" t="str">
-        <v>怪物作防守方时被命中K</v>
+        <v>怪物攻击时暴击倍率幸运K</v>
       </c>
       <c r="J5" s="1" t="str">
-        <v>暴击率基数: Crit/(Crit+K)</v>
+        <v>暴击倍率基数: CritBase + Lucky/(Lucky+K)</v>
       </c>
       <c r="K5" s="1" t="str">
-        <v>英雄攻击时暴击倍率幸运K</v>
+        <v>等级压制-幸运系数</v>
       </c>
       <c r="L5" s="1" t="str">
-        <v>怪物攻击时暴击倍率幸运K</v>
+        <v>等级压制-每级伤害系数</v>
       </c>
       <c r="M5" s="1" t="str">
-        <v>暴击倍率基数: CritBase + Lucky/(Lucky+K)</v>
+        <v>等级压制-幸运系数封顶(人怪两侧一致)</v>
       </c>
       <c r="N5" s="1" t="str">
-        <v>等级压制-英雄防守闪避系数</v>
+        <v>等级压制-英雄防守时伤害最多按几级算</v>
       </c>
       <c r="O5" s="1" t="str">
-        <v>等级压制-英雄防守暴击系数</v>
+        <v>等级压制-怪物防守时伤害最多按几级算</v>
       </c>
       <c r="P5" s="1" t="str">
-        <v>等级压制-怪物防守闪避系数</v>
-      </c>
-      <c r="Q5" s="1" t="str">
-        <v>等级压制-怪物防守暴击系数</v>
-      </c>
-      <c r="R5" s="1" t="str">
-        <v>等级压制-幸运系数</v>
-      </c>
-      <c r="S5" s="1" t="str">
-        <v>等级压制-每级伤害系数</v>
-      </c>
-      <c r="T5" s="1" t="str">
-        <v>等级压制-英雄防守闪避系数封顶</v>
-      </c>
-      <c r="U5" s="1" t="str">
-        <v>等级压制-怪物防守闪避系数封顶</v>
-      </c>
-      <c r="V5" s="1" t="str">
-        <v>等级压制-暴击系数封顶(人怪两侧一致)</v>
-      </c>
-      <c r="W5" s="1" t="str">
-        <v>等级压制-幸运系数封顶(人怪两侧一致)</v>
-      </c>
-      <c r="X5" s="1" t="str">
-        <v>等级压制-英雄防守时伤害最多按几级算</v>
-      </c>
-      <c r="Y5" s="1" t="str">
-        <v>等级压制-怪物防守时伤害最多按几级算</v>
-      </c>
-      <c r="Z5" s="1" t="str">
         <v>无双值上限(旧项目 BaseRoleProperies.gd:20)</v>
       </c>
+      <c r="Q5" s="2" t="str">
+        <v>命中蓄力：伤害/基础攻击×系数；不改变攻击力</v>
+      </c>
+      <c r="R5" s="2" t="str">
+        <v>开启后整招威力倍率（含固定加值）</v>
+      </c>
+      <c r="S5" s="2" t="str">
+        <v>开启后走路、跑步速度倍率</v>
+      </c>
+      <c r="T5" s="2" t="str">
+        <v>开启后起跳速度倍率</v>
+      </c>
+      <c r="U5" s="2" t="str">
+        <v>开启后重力倍率</v>
+      </c>
+      <c r="V5" s="2" t="str">
+        <v>未满时自然衰减（点/秒）；开启期间仍生效</v>
+      </c>
+      <c r="W5" s="2" t="str">
+        <v>开启后额外消耗（点/秒）</v>
+      </c>
+      <c r="X5" s="2" t="str">
+        <v>怪物受击横速每秒保留比例；官方每1/24秒乘0.8，降至移动速度后不再减速</v>
+      </c>
+      <c r="Y5" s="2" t="str">
+        <v>每颗黄色无双球恢复的无双值</v>
+      </c>
+      <c r="Z5" s="2" t="str">
+        <v>每颗蓝球最低回蓝量</v>
+      </c>
       <c r="AA5" s="2" t="str">
-        <v>命中蓄力：伤害/基础攻击×系数；不改变攻击力</v>
+        <v>每颗蓝球按魔法上限恢复的比例</v>
       </c>
       <c r="AB5" s="2" t="str">
-        <v>开启后整招威力倍率（含固定加值）</v>
-      </c>
-      <c r="AC5" s="2" t="str">
-        <v>开启后走路、跑步速度倍率</v>
-      </c>
-      <c r="AD5" s="2" t="str">
-        <v>开启后起跳速度倍率</v>
-      </c>
-      <c r="AE5" s="2" t="str">
-        <v>开启后重力倍率</v>
-      </c>
-      <c r="AF5" s="2" t="str">
-        <v>未满时自然衰减（点/秒）；开启期间仍生效</v>
-      </c>
-      <c r="AG5" s="2" t="str">
-        <v>开启后额外消耗（点/秒）</v>
-      </c>
-      <c r="AH5" s="2" t="str">
-        <v>怪物受击横速每秒保留比例；官方每1/24秒乘0.8，降至移动速度后不再减速</v>
-      </c>
-      <c r="AI5" s="2" t="str">
-        <v>每颗黄色无双球恢复的无双值</v>
-      </c>
-      <c r="AJ5" s="2" t="str">
-        <v>每颗蓝球最低回蓝量</v>
-      </c>
-      <c r="AK5" s="2" t="str">
-        <v>每颗蓝球按魔法上限恢复的比例</v>
-      </c>
-      <c r="AL5" s="2" t="str">
         <v>地面物品保留时间，秒</v>
       </c>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
     </row>
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="1"/>
@@ -739,7 +679,7 @@
         <v>战斗常数</v>
       </c>
       <c r="C6" s="1" t="str">
-        <v>沿用旧项目人怪两侧不一致的基数,集中在此处</v>
+        <v>攻防及伤害沿用项目公式；暴击、闪避采用造一直接概率</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>250</v>
@@ -757,95 +697,75 @@
         <v>100</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="M6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="1" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0.11</v>
-      </c>
       <c r="R6" s="1" t="n">
-        <v>0.07</v>
+        <v>1.5</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>0.05</v>
+        <v>1.5</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U6" s="1" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="V6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>0.7</v>
+        <v>6</v>
       </c>
       <c r="X6" s="1" t="n">
+        <v>0.004722366482869652</v>
+      </c>
+      <c r="Y6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="Y6" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="Z6" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="1" t="n">
-        <v>2</v>
+        <v>0.05</v>
       </c>
       <c r="AB6" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC6" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD6" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE6" s="1" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="AH6" s="1" t="n">
-        <v>0.004722366482869652</v>
-      </c>
-      <c r="AI6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ6" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="AK6" s="1" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AL6" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2252,6 +2172,306 @@
         <v>41.625</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1" t="n">
+        <v>4001</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <v>official.Monster4.hit1</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <v>猕猴王棍击</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <v>原版普通棍击</v>
+      </c>
+      <c r="F25" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <v>30,30</v>
+      </c>
+      <c r="H25" s="1" t="str">
+        <v>Physics</v>
+      </c>
+      <c r="I25" s="1" t="str">
+        <v>144,-120</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="P25" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="Q25" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="R25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="1" t="n">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3"/>
+      <c r="B26" s="1" t="n">
+        <v>4002</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <v>official.Monster4.hit2</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <v>猕猴王旋风</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <v>原版旋转；攻击编号由原生动画方法键更新</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <v>20,20</v>
+      </c>
+      <c r="H26" s="1" t="str">
+        <v>Physics</v>
+      </c>
+      <c r="I26" s="1" t="str">
+        <v>48,-168</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" s="1" t="str">
+        <v>0,150</v>
+      </c>
+      <c r="P26" s="1" t="str">
+        <v>10.833333333333334,10.833333333333334</v>
+      </c>
+      <c r="Q26" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" s="1" t="n">
+        <v>41.625</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1" t="n">
+        <v>4003</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>official.Monster4.hit3</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <v>猕猴王风刃</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <v>原版 Boss2Bullet1 独立攻击</v>
+      </c>
+      <c r="F27" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <v>20,20</v>
+      </c>
+      <c r="H27" s="1" t="str">
+        <v>Magic</v>
+      </c>
+      <c r="I27" s="1" t="str">
+        <v>360,0</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="1" t="str">
+        <v>150,10000</v>
+      </c>
+      <c r="P27" s="1" t="str">
+        <v>7.5,7.5</v>
+      </c>
+      <c r="Q27" s="1" t="str">
+        <v>0.041666666666666664,0.041666666666666664</v>
+      </c>
+      <c r="R27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>41.625</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3"/>
+      <c r="B28" s="1" t="n">
+        <v>6001</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <v>official.Monster6.hit1</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <v>禺狨王杖击</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <v>原版普通杖击</v>
+      </c>
+      <c r="F28" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <v>30,30</v>
+      </c>
+      <c r="H28" s="1" t="str">
+        <v>Physics</v>
+      </c>
+      <c r="I28" s="1" t="str">
+        <v>288,-48</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="str">
+        <v>TamarinKing</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1" t="str">
+        <v>0,250</v>
+      </c>
+      <c r="P28" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="Q28" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="R28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" s="1" t="n">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="1" t="n">
+        <v>6002</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <v>official.Monster6.hit2</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <v>禺狨王落雷</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <v>原版云雷；无敌持续两秒</v>
+      </c>
+      <c r="F29" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <v>40,40</v>
+      </c>
+      <c r="H29" s="1" t="str">
+        <v>Magic</v>
+      </c>
+      <c r="I29" s="1" t="str">
+        <v>48,-288</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="str">
+        <v>TamarinKing</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" s="1" t="str">
+        <v>0,250</v>
+      </c>
+      <c r="P29" s="1" t="str">
+        <v>10,10</v>
+      </c>
+      <c r="Q29" s="1" t="str">
+        <v>0.041666666666666664,0.041666666666666664</v>
+      </c>
+      <c r="R29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1" t="n">
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
